--- a/source_data/Figure4.xlsx
+++ b/source_data/Figure4.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weikangshi/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/weikangshi/Desktop/PostDoc/manuscripts_move_to_dropbox/gaze_accumulation_marmoset_dmPFC/final_after_rebuttal/source_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{144DA8A5-72E6-904B-AF30-4E6141D76A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB1D196-178D-574A-B15C-AA820E7FB4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="5480" windowWidth="28040" windowHeight="17180" xr2:uid="{CDD6E5A6-FA5B-EC4D-9D0B-223207B8A016}"/>
+    <workbookView xWindow="760" yWindow="600" windowWidth="28040" windowHeight="16140" xr2:uid="{CDD6E5A6-FA5B-EC4D-9D0B-223207B8A016}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="panel C" sheetId="1" r:id="rId1"/>
+    <sheet name="panel D" sheetId="2" r:id="rId2"/>
+    <sheet name="panel E" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,15 +37,56 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="10">
+  <si>
+    <t>Corr Coef</t>
+  </si>
+  <si>
+    <t>Animal K</t>
+  </si>
+  <si>
+    <t>Animal D</t>
+  </si>
+  <si>
+    <t>Normalized path variability (local tortuosity)</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>sem</t>
+  </si>
+  <si>
+    <t>shuffle mean</t>
+  </si>
+  <si>
+    <t>shuffle sem</t>
+  </si>
+  <si>
+    <t>succ pull</t>
+  </si>
+  <si>
+    <t>failed pull</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,8 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +450,3158 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{584E4DF8-6FF4-584C-AD7F-D532BD7F03CF}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>-0.110427155998454</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.19675960296007999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>-5.0954152882928903E-3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>-0.149277543765931</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>-0.147039680418771</v>
+      </c>
+      <c r="B5" s="3">
+        <v>-0.160446654056631</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>-0.14252352143585301</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.190384462813533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>-0.220658222980502</v>
+      </c>
+      <c r="B7" s="3">
+        <v>-0.22687263381992401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>-6.2742433738929598E-2</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.13741841377198499</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>9.9767145958592693E-3</v>
+      </c>
+      <c r="B9" s="3">
+        <v>-0.14464304085917901</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>-2.35853054452499E-2</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-0.25286634561600302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>-8.3687725709966996E-3</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-6.7596623391883007E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>-0.17159945439093099</v>
+      </c>
+      <c r="B12" s="3">
+        <v>-0.23854772926307999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>5.40111910616696E-2</v>
+      </c>
+      <c r="B13" s="3">
+        <v>-0.20851703348561701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>-0.29036789194226797</v>
+      </c>
+      <c r="B14" s="3">
+        <v>6.9679089360220006E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>0.120341272427422</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-2.99126741690698E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>-0.29023489058752</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-6.2834780625814296E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>7.7155703810715903E-2</v>
+      </c>
+      <c r="B17" s="3">
+        <v>-0.20852986192640299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>-0.25863182711646399</v>
+      </c>
+      <c r="B18" s="3">
+        <v>-6.7281624264839704E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>-0.289751779739371</v>
+      </c>
+      <c r="B19" s="3">
+        <v>-0.23764856294071901</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>1.3797013871889099E-2</v>
+      </c>
+      <c r="B20" s="3">
+        <v>-0.14378718929029</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>-0.34264400570120601</v>
+      </c>
+      <c r="B21" s="3">
+        <v>-0.33609423861032101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>0.15098062570058801</v>
+      </c>
+      <c r="B22" s="3">
+        <v>9.6228974867622902E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="3">
+        <v>9.5661158076297603E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="3">
+        <v>-5.7982946197380397E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B25" s="3">
+        <v>-0.23608858161726001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" s="3">
+        <v>-4.1356348973930002E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A929947-DE8A-5740-99FD-B1C85A965868}">
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>-0.23831456914139801</v>
+      </c>
+      <c r="B4" s="3">
+        <v>-0.86982777557786395</v>
+      </c>
+      <c r="C4" s="3">
+        <v>-3.8140064867938299E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>-8.9499750341183494E-3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>-0.999999999999999</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.39895118294162E-2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-0.88275793839154504</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>-0.13896814061839199</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.266877478889259</v>
+      </c>
+      <c r="C6" s="3">
+        <v>-0.18834795534068699</v>
+      </c>
+      <c r="D6" s="3">
+        <v>-0.27804271515405399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>-0.122505492471035</v>
+      </c>
+      <c r="B7" s="3">
+        <v>-0.31629002074248103</v>
+      </c>
+      <c r="C7" s="3">
+        <v>-0.23806410471088499</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.53209359670776402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>-0.114313614540652</v>
+      </c>
+      <c r="B8" s="3">
+        <v>-0.67995188877624801</v>
+      </c>
+      <c r="C8" s="3">
+        <v>-6.2520673307707206E-2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.10413992867340301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>-6.3093379235890298E-2</v>
+      </c>
+      <c r="B9" s="3">
+        <v>-0.17668164548075499</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4.6079892304329101E-2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>-0.238482284065517</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>8.1417759295107694E-2</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-2.5581838943756902E-2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-0.23547181067379</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.41548424195883799</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>-0.16059980224137399</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-0.28099650016523697</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-0.118459636713395</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.7827583257675096E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>4.79248660915624E-2</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.30217097885936001</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-0.36436400369530503</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-0.108658238612481</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>-3.3686418104030703E-2</v>
+      </c>
+      <c r="B13" s="3">
+        <v>-0.53939297966006405</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-0.15043180305528001</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-0.418965878142945</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>-0.35289598554142998</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.20643507138490899</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-7.7667608808308905E-2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-0.16495684526079399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>-0.190626518691349</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-0.367489567840735</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-0.10185947434767301</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.64388058886738098</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>-0.17506373991479199</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-0.85904660657234899</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-0.12607725246078599</v>
+      </c>
+      <c r="D16" s="3">
+        <v>8.7569853188589897E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>-0.39571070691194099</v>
+      </c>
+      <c r="B17" s="3">
+        <v>-0.76383266499106806</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-2.3059312768980898E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>-0.17273621315445001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>1.1831058470670701E-2</v>
+      </c>
+      <c r="B18" s="3">
+        <v>-0.22921926004323101</v>
+      </c>
+      <c r="C18" s="3">
+        <v>-0.17882011492734601</v>
+      </c>
+      <c r="D18" s="3">
+        <v>-0.88045573641641095</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>-0.20295702419063999</v>
+      </c>
+      <c r="B19" s="3">
+        <v>-0.85072904580852704</v>
+      </c>
+      <c r="C19" s="3">
+        <v>-0.25026444458236102</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.32197330867192397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>-0.28381988139443598</v>
+      </c>
+      <c r="B20" s="3">
+        <v>-0.46522074959792098</v>
+      </c>
+      <c r="C20" s="3">
+        <v>-0.16860291371864</v>
+      </c>
+      <c r="D20" s="3">
+        <v>-0.96690385452960803</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>3.09339835953155E-2</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.46738522103356001</v>
+      </c>
+      <c r="C21" s="3">
+        <v>8.6453112722163106E-2</v>
+      </c>
+      <c r="D21" s="3">
+        <v>-0.50010393493174599</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>-0.32054627763208898</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.999999999999999</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.113532032821927</v>
+      </c>
+      <c r="D22" s="3">
+        <v>-8.8401021895070195E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>-7.6841913112103102E-2</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.88452859959531904</v>
+      </c>
+      <c r="C23" s="3">
+        <v>-9.3521104875326097E-2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>-0.283014158350826</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C24" s="3">
+        <v>-0.227833703511097</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.39646661624938301</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C25" s="3">
+        <v>5.1896504134775201E-2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>-0.30005526057520399</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D26" s="3">
+        <v>-0.705951108144241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D27" s="3">
+        <v>4.7545135129398203E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FA4252-C504-8642-BAB5-AC074F4172E3}">
+  <dimension ref="A1:H100"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>3.51648696454398E-2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3.7917143778198898E-3</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.52959282127968E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4.5641879517582902E-3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4.72038622840509E-3</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.17372856895502E-2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2.4962940504738101E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>3.5098924266919303E-2</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3.8638904207634198E-3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.64791630942249E-2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4.6652972895195504E-3</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>4.5585311213460896E-3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.21067210394475E-2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2.48029870837614E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>3.7385438848734201E-2</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4.3979229575319204E-3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.9298291248476498E-2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5.1904872513377897E-3</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>4.4692088288057702E-3</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1.3318295666386299E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2.5233169894718901E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>4.0001948375560002E-2</v>
+      </c>
+      <c r="B7" s="3">
+        <v>5.0351603659385697E-3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.1175839583618499E-2</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5.4500869010415103E-3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2.5399999999999999E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.6405731302730704E-3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1.53082955975407E-2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2.7278745234753199E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>4.3657983014258599E-2</v>
+      </c>
+      <c r="B8" s="3">
+        <v>6.0752569047446397E-3</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2.3250086673055101E-2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5.7665046625948501E-3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.9416925992766996E-3</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1.7497813471352801E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2.8873509118982998E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>4.7469066953233802E-2</v>
+      </c>
+      <c r="B9" s="3">
+        <v>7.1212725665194196E-3</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2.5378402834671101E-2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6.2279840370420099E-3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5.3927249727940899E-3</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.99982719904719E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3.2167158429971402E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>5.1653642224858999E-2</v>
+      </c>
+      <c r="B10" s="3">
+        <v>8.1512996620015706E-3</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.73424617748819E-2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6.6274650925054997E-3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6.0481018282954003E-3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2.2431112117059102E-2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3.78147212210478E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>5.5636496919386901E-2</v>
+      </c>
+      <c r="B11" s="3">
+        <v>8.83925485945403E-3</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.8907521528855298E-2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6.8920467859254096E-3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.32E-2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6.4020402915825701E-3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2.4792855614014699E-2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>4.21697010971095E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>5.8362985838114299E-2</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9.0146082614184705E-3</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.03885077996724E-2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7.3647067655622503E-3</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>6.8080565230565103E-3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2.7057109119068799E-2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>4.4727391351576298E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>5.95986285423203E-2</v>
+      </c>
+      <c r="B13" s="3">
+        <v>8.9319401958101296E-3</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.0299752307274601E-2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7.3908818541595003E-3</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>7.0591769835758496E-3</v>
+      </c>
+      <c r="G13" s="3">
+        <v>2.7646448413643301E-2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>4.6593057004146801E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>5.9265482813964397E-2</v>
+      </c>
+      <c r="B14" s="3">
+        <v>8.7056663013085397E-3</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.0755427282721199E-2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>7.5290568993779403E-3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3.8300000000000001E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>7.2142801842359E-3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2.8198580520903599E-2</v>
+      </c>
+      <c r="H14" s="3">
+        <v>4.6625952812450397E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>5.8431306688532303E-2</v>
+      </c>
+      <c r="B15" s="3">
+        <v>8.4061133314354605E-3</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.12744734253943E-2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>7.7605633792434698E-3</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>7.3701846030225998E-3</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2.85839534600895E-2</v>
+      </c>
+      <c r="H15" s="3">
+        <v>4.8441600842379102E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>5.6200862359433501E-2</v>
+      </c>
+      <c r="B16" s="3">
+        <v>8.3382526175025205E-3</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.2401871568784602E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>8.0188834617582697E-3</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>7.51522242231965E-3</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2.8553058154042101E-2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>5.0872736050761799E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>5.4478059218767402E-2</v>
+      </c>
+      <c r="B17" s="3">
+        <v>8.3433249212341402E-3</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.41377692595509E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.4830857940447705E-3</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>7.4113518812576303E-3</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2.7925904316526199E-2</v>
+      </c>
+      <c r="H17" s="3">
+        <v>5.3392817871247599E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>5.3697280704809197E-2</v>
+      </c>
+      <c r="B18" s="3">
+        <v>8.6984033310468292E-3</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3.5798362608442602E-2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>8.9468476830532207E-3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>7.4030393407511904E-3</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2.7605291659522999E-2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>5.5321845941923697E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>5.29853939451113E-2</v>
+      </c>
+      <c r="B19" s="3">
+        <v>9.0695841437187907E-3</v>
+      </c>
+      <c r="C19" s="3">
+        <v>3.7725642963867698E-2</v>
+      </c>
+      <c r="D19" s="3">
+        <v>9.3411410353772296E-3</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>7.1514208756138804E-3</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2.73023187621915E-2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>5.4434599338796996E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>5.3045451443201601E-2</v>
+      </c>
+      <c r="B20" s="3">
+        <v>9.57204056596281E-3</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3.8908602161996299E-2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>9.6266894352828002E-3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>6.9671561781033996E-3</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2.73705617487589E-2</v>
+      </c>
+      <c r="H20" s="3">
+        <v>5.3741310188242302E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>5.3069071980439399E-2</v>
+      </c>
+      <c r="B21" s="3">
+        <v>9.5813450716647208E-3</v>
+      </c>
+      <c r="C21" s="3">
+        <v>3.9702941216084003E-2</v>
+      </c>
+      <c r="D21" s="3">
+        <v>9.8434485624565096E-3</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>6.8635984550238704E-3</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2.6745748499032999E-2</v>
+      </c>
+      <c r="H21" s="3">
+        <v>5.1406599846584699E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>5.4401154992834599E-2</v>
+      </c>
+      <c r="B22" s="3">
+        <v>9.7166851928011597E-3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>3.9707140092077903E-2</v>
+      </c>
+      <c r="D22" s="3">
+        <v>9.82230748283619E-3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3.78E-2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>6.9255313498928703E-3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2.6513181988360199E-2</v>
+      </c>
+      <c r="H22" s="3">
+        <v>4.7655130562455897E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>5.3981844345612803E-2</v>
+      </c>
+      <c r="B23" s="3">
+        <v>9.4721786505519798E-3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>3.9264498176304799E-2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>9.7684909186684897E-3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="F23" s="3">
+        <v>7.5060747096664399E-3</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2.6833736333996001E-2</v>
+      </c>
+      <c r="H23" s="3">
+        <v>4.9581109138287097E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>5.4452006204528502E-2</v>
+      </c>
+      <c r="B24" s="3">
+        <v>9.3636274676569802E-3</v>
+      </c>
+      <c r="C24" s="3">
+        <v>3.8022129057014901E-2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>9.5035291780339193E-3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="F24" s="3">
+        <v>7.9153505331146599E-3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2.6735169778994001E-2</v>
+      </c>
+      <c r="H24" s="3">
+        <v>5.1540331198648096E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>5.5301263964997703E-2</v>
+      </c>
+      <c r="B25" s="3">
+        <v>9.6142057391565595E-3</v>
+      </c>
+      <c r="C25" s="3">
+        <v>3.63408682193379E-2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>9.0923847860564996E-3</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>8.1755134204543698E-3</v>
+      </c>
+      <c r="G25" s="3">
+        <v>2.6840833599823598E-2</v>
+      </c>
+      <c r="H25" s="3">
+        <v>5.4441355847413501E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <v>5.5622107296358601E-2</v>
+      </c>
+      <c r="B26" s="3">
+        <v>9.6321040602290308E-3</v>
+      </c>
+      <c r="C26" s="3">
+        <v>3.38901524836508E-2</v>
+      </c>
+      <c r="D26" s="3">
+        <v>8.5841514280058893E-3</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4.24E-2</v>
+      </c>
+      <c r="F26" s="3">
+        <v>8.5332469965274903E-3</v>
+      </c>
+      <c r="G26" s="3">
+        <v>2.6905510006577701E-2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>5.6634963825158199E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>5.5508887589602401E-2</v>
+      </c>
+      <c r="B27" s="3">
+        <v>9.6342941021072496E-3</v>
+      </c>
+      <c r="C27" s="3">
+        <v>3.2445709970718099E-2</v>
+      </c>
+      <c r="D27" s="3">
+        <v>8.0915675414683502E-3</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="F27" s="3">
+        <v>8.7149367233211004E-3</v>
+      </c>
+      <c r="G27" s="3">
+        <v>2.7346343575765299E-2</v>
+      </c>
+      <c r="H27" s="3">
+        <v>5.8066441189622304E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>5.5317741254146499E-2</v>
+      </c>
+      <c r="B28" s="3">
+        <v>9.4886922392817697E-3</v>
+      </c>
+      <c r="C28" s="3">
+        <v>3.1151074254870199E-2</v>
+      </c>
+      <c r="D28" s="3">
+        <v>7.8226132781678299E-3</v>
+      </c>
+      <c r="E28" s="3">
+        <v>4.24E-2</v>
+      </c>
+      <c r="F28" s="3">
+        <v>8.5183823634140295E-3</v>
+      </c>
+      <c r="G28" s="3">
+        <v>2.7704268738326099E-2</v>
+      </c>
+      <c r="H28" s="3">
+        <v>5.9060547497928797E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>5.4827467127949003E-2</v>
+      </c>
+      <c r="B29" s="3">
+        <v>9.1372359517370508E-3</v>
+      </c>
+      <c r="C29" s="3">
+        <v>3.0610852492897699E-2</v>
+      </c>
+      <c r="D29" s="3">
+        <v>8.14007983672458E-3</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="F29" s="3">
+        <v>8.1959921104572397E-3</v>
+      </c>
+      <c r="G29" s="3">
+        <v>2.72531694498299E-2</v>
+      </c>
+      <c r="H29" s="3">
+        <v>5.8779479810253197E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>5.3170353040134899E-2</v>
+      </c>
+      <c r="B30" s="3">
+        <v>8.5752724809804708E-3</v>
+      </c>
+      <c r="C30" s="3">
+        <v>3.06814509210016E-2</v>
+      </c>
+      <c r="D30" s="3">
+        <v>8.39501276855497E-3</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="F30" s="3">
+        <v>7.7230710253454703E-3</v>
+      </c>
+      <c r="G30" s="3">
+        <v>2.71407490956883E-2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>5.6066132522457103E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>5.1136082440371697E-2</v>
+      </c>
+      <c r="B31" s="3">
+        <v>8.0155325693582608E-3</v>
+      </c>
+      <c r="C31" s="3">
+        <v>3.0706549863909301E-2</v>
+      </c>
+      <c r="D31" s="3">
+        <v>8.6155360313792395E-3</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="F31" s="3">
+        <v>7.1978288956393499E-3</v>
+      </c>
+      <c r="G31" s="3">
+        <v>2.7801804504361701E-2</v>
+      </c>
+      <c r="H31" s="3">
+        <v>5.61825400696886E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>4.8189260874634099E-2</v>
+      </c>
+      <c r="B32" s="3">
+        <v>7.2922407252833396E-3</v>
+      </c>
+      <c r="C32" s="3">
+        <v>3.1852003649062398E-2</v>
+      </c>
+      <c r="D32" s="3">
+        <v>8.7612099972869794E-3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>3.95E-2</v>
+      </c>
+      <c r="F32" s="3">
+        <v>6.5759398729070698E-3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>2.7928417372430799E-2</v>
+      </c>
+      <c r="H32" s="3">
+        <v>5.7488491271333103E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>4.63586901328134E-2</v>
+      </c>
+      <c r="B33" s="3">
+        <v>7.0063774474618699E-3</v>
+      </c>
+      <c r="C33" s="3">
+        <v>3.2962152652457999E-2</v>
+      </c>
+      <c r="D33" s="3">
+        <v>9.1632705371852297E-3</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="F33" s="3">
+        <v>6.1202731132036199E-3</v>
+      </c>
+      <c r="G33" s="3">
+        <v>2.8991098238332399E-2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>5.9285662296973997E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>4.3746405042256901E-2</v>
+      </c>
+      <c r="B34" s="3">
+        <v>6.6339047403308404E-3</v>
+      </c>
+      <c r="C34" s="3">
+        <v>3.4945700516654098E-2</v>
+      </c>
+      <c r="D34" s="3">
+        <v>9.68744054545965E-3</v>
+      </c>
+      <c r="E34" s="3">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="F34" s="3">
+        <v>6.0710226705606701E-3</v>
+      </c>
+      <c r="G34" s="3">
+        <v>3.1150683194499901E-2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>6.5354995759101002E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>4.06755259153707E-2</v>
+      </c>
+      <c r="B35" s="3">
+        <v>6.05191183593676E-3</v>
+      </c>
+      <c r="C35" s="3">
+        <v>3.58597710382762E-2</v>
+      </c>
+      <c r="D35" s="3">
+        <v>9.6929688678827203E-3</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3.7400000000000003E-2</v>
+      </c>
+      <c r="F35" s="3">
+        <v>5.9343933752336996E-3</v>
+      </c>
+      <c r="G35" s="3">
+        <v>3.3242145255974402E-2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>7.0033137013353697E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>3.93615236759845E-2</v>
+      </c>
+      <c r="B36" s="3">
+        <v>5.9751727984041101E-3</v>
+      </c>
+      <c r="C36" s="3">
+        <v>3.6172098826622499E-2</v>
+      </c>
+      <c r="D36" s="3">
+        <v>9.56278278048814E-3</v>
+      </c>
+      <c r="E36" s="3">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="F36" s="3">
+        <v>5.7770822426059798E-3</v>
+      </c>
+      <c r="G36" s="3">
+        <v>3.4973864602655898E-2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>7.8151978199816306E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>3.8428740450163999E-2</v>
+      </c>
+      <c r="B37" s="3">
+        <v>5.8951581856532802E-3</v>
+      </c>
+      <c r="C37" s="3">
+        <v>3.6237283857543101E-2</v>
+      </c>
+      <c r="D37" s="3">
+        <v>9.5481561565191192E-3</v>
+      </c>
+      <c r="E37" s="3">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="F37" s="3">
+        <v>5.8205785521670203E-3</v>
+      </c>
+      <c r="G37" s="3">
+        <v>3.5990467309285901E-2</v>
+      </c>
+      <c r="H37" s="3">
+        <v>8.2454913972973502E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>3.7484895509280698E-2</v>
+      </c>
+      <c r="B38" s="3">
+        <v>5.8826805760141699E-3</v>
+      </c>
+      <c r="C38" s="3">
+        <v>3.6018589533288597E-2</v>
+      </c>
+      <c r="D38" s="3">
+        <v>9.2080850232372693E-3</v>
+      </c>
+      <c r="E38" s="3">
+        <v>3.56E-2</v>
+      </c>
+      <c r="F38" s="3">
+        <v>5.8055992447163998E-3</v>
+      </c>
+      <c r="G38" s="3">
+        <v>3.6040671567556602E-2</v>
+      </c>
+      <c r="H38" s="3">
+        <v>8.3950168139386803E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>3.7108309285412103E-2</v>
+      </c>
+      <c r="B39" s="3">
+        <v>5.7963466895656702E-3</v>
+      </c>
+      <c r="C39" s="3">
+        <v>3.4907230659610301E-2</v>
+      </c>
+      <c r="D39" s="3">
+        <v>8.7013348338529795E-3</v>
+      </c>
+      <c r="E39" s="3">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="F39" s="3">
+        <v>5.7330402673097204E-3</v>
+      </c>
+      <c r="G39" s="3">
+        <v>3.5442656174904302E-2</v>
+      </c>
+      <c r="H39" s="3">
+        <v>8.4358547950706096E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>3.7003185267923303E-2</v>
+      </c>
+      <c r="B40" s="3">
+        <v>5.8941992478840502E-3</v>
+      </c>
+      <c r="C40" s="3">
+        <v>3.4171933435898E-2</v>
+      </c>
+      <c r="D40" s="3">
+        <v>8.5641267093310193E-3</v>
+      </c>
+      <c r="E40" s="3">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="F40" s="3">
+        <v>6.1189314175971801E-3</v>
+      </c>
+      <c r="G40" s="3">
+        <v>3.3411992054982097E-2</v>
+      </c>
+      <c r="H40" s="3">
+        <v>8.15567607680962E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <v>3.8038199897809502E-2</v>
+      </c>
+      <c r="B41" s="3">
+        <v>6.0904384535602797E-3</v>
+      </c>
+      <c r="C41" s="3">
+        <v>3.5448535611798497E-2</v>
+      </c>
+      <c r="D41" s="3">
+        <v>8.9277338444208702E-3</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="F41" s="3">
+        <v>6.2792900746923399E-3</v>
+      </c>
+      <c r="G41" s="3">
+        <v>3.0775347393627001E-2</v>
+      </c>
+      <c r="H41" s="3">
+        <v>7.52489362188879E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>3.89912990952649E-2</v>
+      </c>
+      <c r="B42" s="3">
+        <v>6.5652590244919201E-3</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3.5290170547320802E-2</v>
+      </c>
+      <c r="D42" s="3">
+        <v>9.1424757339281792E-3</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="F42" s="3">
+        <v>6.5659380706674904E-3</v>
+      </c>
+      <c r="G42" s="3">
+        <v>2.8438266423426201E-2</v>
+      </c>
+      <c r="H42" s="3">
+        <v>6.7819623055100902E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <v>4.01915559005315E-2</v>
+      </c>
+      <c r="B43" s="3">
+        <v>7.1566334196572403E-3</v>
+      </c>
+      <c r="C43" s="3">
+        <v>3.6780811145547501E-2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>9.2757331143348293E-3</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="F43" s="3">
+        <v>6.8757145104485903E-3</v>
+      </c>
+      <c r="G43" s="3">
+        <v>2.6278828126858601E-2</v>
+      </c>
+      <c r="H43" s="3">
+        <v>6.2169682281699098E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>4.21387804494378E-2</v>
+      </c>
+      <c r="B44" s="3">
+        <v>7.5662239426507599E-3</v>
+      </c>
+      <c r="C44" s="3">
+        <v>3.7112270124350401E-2</v>
+      </c>
+      <c r="D44" s="3">
+        <v>9.3959592861008606E-3</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="F44" s="3">
+        <v>7.0983577580675901E-3</v>
+      </c>
+      <c r="G44" s="3">
+        <v>2.4114654773712E-2</v>
+      </c>
+      <c r="H44" s="3">
+        <v>5.4177146821363098E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>4.3275880606552401E-2</v>
+      </c>
+      <c r="B45" s="3">
+        <v>7.8118924852604004E-3</v>
+      </c>
+      <c r="C45" s="3">
+        <v>3.7772621184591897E-2</v>
+      </c>
+      <c r="D45" s="3">
+        <v>9.5572969028448595E-3</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="F45" s="3">
+        <v>7.26906670401695E-3</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2.3075760578960301E-2</v>
+      </c>
+      <c r="H45" s="3">
+        <v>5.0768324846098296E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>4.3345083383783803E-2</v>
+      </c>
+      <c r="B46" s="3">
+        <v>7.7480096484959403E-3</v>
+      </c>
+      <c r="C46" s="3">
+        <v>3.8408417511609602E-2</v>
+      </c>
+      <c r="D46" s="3">
+        <v>9.5926893186141608E-3</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="F46" s="3">
+        <v>7.25794811134833E-3</v>
+      </c>
+      <c r="G46" s="3">
+        <v>2.2746331020296499E-2</v>
+      </c>
+      <c r="H46" s="3">
+        <v>4.8129192671553002E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>4.3778283553997703E-2</v>
+      </c>
+      <c r="B47" s="3">
+        <v>7.4722013924736503E-3</v>
+      </c>
+      <c r="C47" s="3">
+        <v>3.7649531959695698E-2</v>
+      </c>
+      <c r="D47" s="3">
+        <v>9.2138357097342298E-3</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="F47" s="3">
+        <v>7.1842627016117204E-3</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2.3476700554633401E-2</v>
+      </c>
+      <c r="H47" s="3">
+        <v>4.82895395699336E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>4.2620651003228302E-2</v>
+      </c>
+      <c r="B48" s="3">
+        <v>6.83333063924334E-3</v>
+      </c>
+      <c r="C48" s="3">
+        <v>3.6899971147473599E-2</v>
+      </c>
+      <c r="D48" s="3">
+        <v>8.6475848343944006E-3</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="F48" s="3">
+        <v>7.0601446153118899E-3</v>
+      </c>
+      <c r="G48" s="3">
+        <v>2.3737007801091999E-2</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4.8840254959457204E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>4.1074039732142999E-2</v>
+      </c>
+      <c r="B49" s="3">
+        <v>6.2663448589475304E-3</v>
+      </c>
+      <c r="C49" s="3">
+        <v>3.6263832450077603E-2</v>
+      </c>
+      <c r="D49" s="3">
+        <v>8.1256342221547907E-3</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="F49" s="3">
+        <v>6.8936304997095198E-3</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2.3963408206664299E-2</v>
+      </c>
+      <c r="H49" s="3">
+        <v>4.9186678074955798E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>3.8763163652630002E-2</v>
+      </c>
+      <c r="B50" s="3">
+        <v>5.5436545435397604E-3</v>
+      </c>
+      <c r="C50" s="3">
+        <v>3.5947155611647102E-2</v>
+      </c>
+      <c r="D50" s="3">
+        <v>7.8690429689345694E-3</v>
+      </c>
+      <c r="E50" s="3">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="F50" s="3">
+        <v>6.5755315577732797E-3</v>
+      </c>
+      <c r="G50" s="3">
+        <v>2.4730006603108499E-2</v>
+      </c>
+      <c r="H50" s="3">
+        <v>5.1415615654743603E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>3.6362306649023103E-2</v>
+      </c>
+      <c r="B51" s="3">
+        <v>5.1897195648544199E-3</v>
+      </c>
+      <c r="C51" s="3">
+        <v>3.4225997646120603E-2</v>
+      </c>
+      <c r="D51" s="3">
+        <v>7.5432243082277101E-3</v>
+      </c>
+      <c r="E51" s="3">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F51" s="3">
+        <v>6.46785320466406E-3</v>
+      </c>
+      <c r="G51" s="3">
+        <v>2.45132952216831E-2</v>
+      </c>
+      <c r="H51" s="3">
+        <v>5.1779544220937803E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>3.4932172922803303E-2</v>
+      </c>
+      <c r="B52" s="3">
+        <v>4.88306291277353E-3</v>
+      </c>
+      <c r="C52" s="3">
+        <v>3.4570973124885898E-2</v>
+      </c>
+      <c r="D52" s="3">
+        <v>7.7254595400301504E-3</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3.44E-2</v>
+      </c>
+      <c r="F52" s="3">
+        <v>6.2261078617822999E-3</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2.4019241756615298E-2</v>
+      </c>
+      <c r="H52" s="3">
+        <v>5.2270654096899802E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>3.34669179313202E-2</v>
+      </c>
+      <c r="B53" s="3">
+        <v>4.5892152633094001E-3</v>
+      </c>
+      <c r="C53" s="3">
+        <v>3.5427678980907602E-2</v>
+      </c>
+      <c r="D53" s="3">
+        <v>8.1054796316770497E-3</v>
+      </c>
+      <c r="E53" s="3">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="F53" s="3">
+        <v>6.6069513828810296E-3</v>
+      </c>
+      <c r="G53" s="3">
+        <v>2.31775453635743E-2</v>
+      </c>
+      <c r="H53" s="3">
+        <v>5.1353559959266201E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>3.2439842616571998E-2</v>
+      </c>
+      <c r="B54" s="3">
+        <v>4.6154378480288997E-3</v>
+      </c>
+      <c r="C54" s="3">
+        <v>3.6630448688068799E-2</v>
+      </c>
+      <c r="D54" s="3">
+        <v>8.4623970863521806E-3</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="F54" s="3">
+        <v>7.0437419562250098E-3</v>
+      </c>
+      <c r="G54" s="3">
+        <v>2.2327237983177199E-2</v>
+      </c>
+      <c r="H54" s="3">
+        <v>5.0626699821042596E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>3.2706595036438101E-2</v>
+      </c>
+      <c r="B55" s="3">
+        <v>4.8298183023375999E-3</v>
+      </c>
+      <c r="C55" s="3">
+        <v>3.6949589110515602E-2</v>
+      </c>
+      <c r="D55" s="3">
+        <v>8.7185229995843105E-3</v>
+      </c>
+      <c r="E55" s="3">
+        <v>3.78E-2</v>
+      </c>
+      <c r="F55" s="3">
+        <v>7.4016383559154303E-3</v>
+      </c>
+      <c r="G55" s="3">
+        <v>2.17166485026213E-2</v>
+      </c>
+      <c r="H55" s="3">
+        <v>4.98670151959102E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <v>3.2835955583036897E-2</v>
+      </c>
+      <c r="B56" s="3">
+        <v>4.9252586564046599E-3</v>
+      </c>
+      <c r="C56" s="3">
+        <v>3.7191668219276199E-2</v>
+      </c>
+      <c r="D56" s="3">
+        <v>8.9398774230842505E-3</v>
+      </c>
+      <c r="E56" s="3">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="F56" s="3">
+        <v>7.6299077600911498E-3</v>
+      </c>
+      <c r="G56" s="3">
+        <v>2.1138105061764299E-2</v>
+      </c>
+      <c r="H56" s="3">
+        <v>4.6650369158519004E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <v>3.2939826075126598E-2</v>
+      </c>
+      <c r="B57" s="3">
+        <v>5.0860228875580704E-3</v>
+      </c>
+      <c r="C57" s="3">
+        <v>3.8101513060438297E-2</v>
+      </c>
+      <c r="D57" s="3">
+        <v>9.3971202665921998E-3</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="F57" s="3">
+        <v>7.7692085130201703E-3</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2.0459843784740101E-2</v>
+      </c>
+      <c r="H57" s="3">
+        <v>4.3684097823938001E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
+        <v>3.3813056847772902E-2</v>
+      </c>
+      <c r="B58" s="3">
+        <v>5.3177884099010198E-3</v>
+      </c>
+      <c r="C58" s="3">
+        <v>3.7940655032953401E-2</v>
+      </c>
+      <c r="D58" s="3">
+        <v>9.7843422219413504E-3</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="F58" s="3">
+        <v>7.61541526345669E-3</v>
+      </c>
+      <c r="G58" s="3">
+        <v>2.26180557732839E-2</v>
+      </c>
+      <c r="H58" s="3">
+        <v>4.53601841153029E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
+        <v>3.4150115179546803E-2</v>
+      </c>
+      <c r="B59" s="3">
+        <v>5.5233842655773796E-3</v>
+      </c>
+      <c r="C59" s="3">
+        <v>3.76470436686712E-2</v>
+      </c>
+      <c r="D59" s="3">
+        <v>9.8902049825504001E-3</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="F59" s="3">
+        <v>7.5364082042090903E-3</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2.42443896937105E-2</v>
+      </c>
+      <c r="H59" s="3">
+        <v>4.6388064949823699E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
+        <v>3.4313640174648399E-2</v>
+      </c>
+      <c r="B60" s="3">
+        <v>5.6461925897452296E-3</v>
+      </c>
+      <c r="C60" s="3">
+        <v>3.7785604254229201E-2</v>
+      </c>
+      <c r="D60" s="3">
+        <v>1.02426410274439E-2</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="F60" s="3">
+        <v>7.33929219725482E-3</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2.5272330007597901E-2</v>
+      </c>
+      <c r="H60" s="3">
+        <v>4.6137828552881097E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="3">
+        <v>3.4089096969664098E-2</v>
+      </c>
+      <c r="B61" s="3">
+        <v>5.5965232014841201E-3</v>
+      </c>
+      <c r="C61" s="3">
+        <v>3.7761796723675398E-2</v>
+      </c>
+      <c r="D61" s="3">
+        <v>1.05278907029954E-2</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="F61" s="3">
+        <v>7.3779947199764497E-3</v>
+      </c>
+      <c r="G61" s="3">
+        <v>2.71781448000116E-2</v>
+      </c>
+      <c r="H61" s="3">
+        <v>4.8970815909774503E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
+        <v>3.3998071206094299E-2</v>
+      </c>
+      <c r="B62" s="3">
+        <v>5.6272010212992203E-3</v>
+      </c>
+      <c r="C62" s="3">
+        <v>3.7490471355259798E-2</v>
+      </c>
+      <c r="D62" s="3">
+        <v>1.0921460461373E-2</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="F62" s="3">
+        <v>6.9983544917673196E-3</v>
+      </c>
+      <c r="G62" s="3">
+        <v>2.8692753929405401E-2</v>
+      </c>
+      <c r="H62" s="3">
+        <v>4.9987852800906602E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
+        <v>3.3896163132880498E-2</v>
+      </c>
+      <c r="B63" s="3">
+        <v>5.5646374171765996E-3</v>
+      </c>
+      <c r="C63" s="3">
+        <v>3.6310298395202903E-2</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1.09442307258321E-2</v>
+      </c>
+      <c r="E63" s="3">
+        <v>3.56E-2</v>
+      </c>
+      <c r="F63" s="3">
+        <v>6.3255506535597403E-3</v>
+      </c>
+      <c r="G63" s="3">
+        <v>2.9293267047080199E-2</v>
+      </c>
+      <c r="H63" s="3">
+        <v>5.0346820422072103E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
+        <v>3.3651710261834201E-2</v>
+      </c>
+      <c r="B64" s="3">
+        <v>5.3848474006485698E-3</v>
+      </c>
+      <c r="C64" s="3">
+        <v>3.59381190922822E-2</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1.0895298009050701E-2</v>
+      </c>
+      <c r="E64" s="3">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="F64" s="3">
+        <v>5.7995702292615798E-3</v>
+      </c>
+      <c r="G64" s="3">
+        <v>2.8985646922000698E-2</v>
+      </c>
+      <c r="H64" s="3">
+        <v>4.9905354538740702E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="3">
+        <v>3.3240109846495502E-2</v>
+      </c>
+      <c r="B65" s="3">
+        <v>5.2593758231138802E-3</v>
+      </c>
+      <c r="C65" s="3">
+        <v>3.5871793995301E-2</v>
+      </c>
+      <c r="D65" s="3">
+        <v>1.06199687547078E-2</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="F65" s="3">
+        <v>5.5009357154831399E-3</v>
+      </c>
+      <c r="G65" s="3">
+        <v>2.80596812975905E-2</v>
+      </c>
+      <c r="H65" s="3">
+        <v>4.8002256379578402E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="3">
+        <v>3.3168705960338697E-2</v>
+      </c>
+      <c r="B66" s="3">
+        <v>5.2387256637773903E-3</v>
+      </c>
+      <c r="C66" s="3">
+        <v>3.5364045324422499E-2</v>
+      </c>
+      <c r="D66" s="3">
+        <v>1.03535749523237E-2</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="F66" s="3">
+        <v>5.7032891702078403E-3</v>
+      </c>
+      <c r="G66" s="3">
+        <v>2.7574409656541499E-2</v>
+      </c>
+      <c r="H66" s="3">
+        <v>4.8825250775314097E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <v>3.2590002642615197E-2</v>
+      </c>
+      <c r="B67" s="3">
+        <v>5.1509226122569201E-3</v>
+      </c>
+      <c r="C67" s="3">
+        <v>3.4302491665703802E-2</v>
+      </c>
+      <c r="D67" s="3">
+        <v>9.6504159738105694E-3</v>
+      </c>
+      <c r="E67" s="3">
+        <v>2.87E-2</v>
+      </c>
+      <c r="F67" s="3">
+        <v>5.8348393668414301E-3</v>
+      </c>
+      <c r="G67" s="3">
+        <v>2.6894674972038301E-2</v>
+      </c>
+      <c r="H67" s="3">
+        <v>4.9569105706879796E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <v>3.25363651605678E-2</v>
+      </c>
+      <c r="B68" s="3">
+        <v>4.9412765271709099E-3</v>
+      </c>
+      <c r="C68" s="3">
+        <v>3.3776654780584697E-2</v>
+      </c>
+      <c r="D68" s="3">
+        <v>9.2654972933054903E-3</v>
+      </c>
+      <c r="E68" s="3">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="F68" s="3">
+        <v>5.91509168709849E-3</v>
+      </c>
+      <c r="G68" s="3">
+        <v>2.51614931128065E-2</v>
+      </c>
+      <c r="H68" s="3">
+        <v>5.1001244258061101E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <v>3.28010950675885E-2</v>
+      </c>
+      <c r="B69" s="3">
+        <v>5.01916982615768E-3</v>
+      </c>
+      <c r="C69" s="3">
+        <v>3.3729080709625998E-2</v>
+      </c>
+      <c r="D69" s="3">
+        <v>9.1115351142514508E-3</v>
+      </c>
+      <c r="E69" s="3">
+        <v>2.53E-2</v>
+      </c>
+      <c r="F69" s="3">
+        <v>5.8514023409120498E-3</v>
+      </c>
+      <c r="G69" s="3">
+        <v>2.5005371154840601E-2</v>
+      </c>
+      <c r="H69" s="3">
+        <v>5.1866721968981599E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <v>3.38353092334433E-2</v>
+      </c>
+      <c r="B70" s="3">
+        <v>4.9402094690920804E-3</v>
+      </c>
+      <c r="C70" s="3">
+        <v>3.3093535866040302E-2</v>
+      </c>
+      <c r="D70" s="3">
+        <v>8.7626246672313102E-3</v>
+      </c>
+      <c r="E70" s="3">
+        <v>2.47E-2</v>
+      </c>
+      <c r="F70" s="3">
+        <v>5.7367198681550604E-3</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2.5044131094984601E-2</v>
+      </c>
+      <c r="H70" s="3">
+        <v>5.2701791754691703E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <v>3.4205192705298801E-2</v>
+      </c>
+      <c r="B71" s="3">
+        <v>4.9010230463275703E-3</v>
+      </c>
+      <c r="C71" s="3">
+        <v>3.4396624845923797E-2</v>
+      </c>
+      <c r="D71" s="3">
+        <v>8.7900057412571304E-3</v>
+      </c>
+      <c r="E71" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="F71" s="3">
+        <v>5.5828937204671003E-3</v>
+      </c>
+      <c r="G71" s="3">
+        <v>2.4713619497730599E-2</v>
+      </c>
+      <c r="H71" s="3">
+        <v>5.2055128311587796E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
+        <v>3.4304396966081299E-2</v>
+      </c>
+      <c r="B72" s="3">
+        <v>4.8163846319132899E-3</v>
+      </c>
+      <c r="C72" s="3">
+        <v>3.6431082901186698E-2</v>
+      </c>
+      <c r="D72" s="3">
+        <v>8.74195261855399E-3</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="F72" s="3">
+        <v>5.45588127449131E-3</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2.39486271028303E-2</v>
+      </c>
+      <c r="H72" s="3">
+        <v>4.9858970603785698E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <v>3.5171169917460998E-2</v>
+      </c>
+      <c r="B73" s="3">
+        <v>4.9394898893397998E-3</v>
+      </c>
+      <c r="C73" s="3">
+        <v>3.7776104340365102E-2</v>
+      </c>
+      <c r="D73" s="3">
+        <v>8.7746587802587008E-3</v>
+      </c>
+      <c r="E73" s="3">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="F73" s="3">
+        <v>5.1577483244287696E-3</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2.3607206250219101E-2</v>
+      </c>
+      <c r="H73" s="3">
+        <v>4.6284434750364497E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <v>3.50461370595396E-2</v>
+      </c>
+      <c r="B74" s="3">
+        <v>4.9614518590591098E-3</v>
+      </c>
+      <c r="C74" s="3">
+        <v>3.9748917994730897E-2</v>
+      </c>
+      <c r="D74" s="3">
+        <v>8.8410995549421598E-3</v>
+      </c>
+      <c r="E74" s="3">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F74" s="3">
+        <v>5.0558822870072498E-3</v>
+      </c>
+      <c r="G74" s="3">
+        <v>2.3072236161858901E-2</v>
+      </c>
+      <c r="H74" s="3">
+        <v>4.1496517054281003E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <v>3.4582124998229102E-2</v>
+      </c>
+      <c r="B75" s="3">
+        <v>4.95153004091537E-3</v>
+      </c>
+      <c r="C75" s="3">
+        <v>4.15037711088855E-2</v>
+      </c>
+      <c r="D75" s="3">
+        <v>8.9929332232306005E-3</v>
+      </c>
+      <c r="E75" s="3">
+        <v>2.29E-2</v>
+      </c>
+      <c r="F75" s="3">
+        <v>4.8264214487786202E-3</v>
+      </c>
+      <c r="G75" s="3">
+        <v>2.2839023767695199E-2</v>
+      </c>
+      <c r="H75" s="3">
+        <v>3.89954884788452E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <v>3.4005157634319702E-2</v>
+      </c>
+      <c r="B76" s="3">
+        <v>4.9640442837212201E-3</v>
+      </c>
+      <c r="C76" s="3">
+        <v>4.2313330943863102E-2</v>
+      </c>
+      <c r="D76" s="3">
+        <v>8.6930754982888492E-3</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="F76" s="3">
+        <v>4.4744780641942901E-3</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2.29881017906137E-2</v>
+      </c>
+      <c r="H76" s="3">
+        <v>3.9049032044498801E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <v>3.2925632570875503E-2</v>
+      </c>
+      <c r="B77" s="3">
+        <v>4.8803669002480399E-3</v>
+      </c>
+      <c r="C77" s="3">
+        <v>4.2447259220420301E-2</v>
+      </c>
+      <c r="D77" s="3">
+        <v>8.6108575853661492E-3</v>
+      </c>
+      <c r="E77" s="3">
+        <v>2.23E-2</v>
+      </c>
+      <c r="F77" s="3">
+        <v>4.3795356883968399E-3</v>
+      </c>
+      <c r="G77" s="3">
+        <v>2.3070029397733099E-2</v>
+      </c>
+      <c r="H77" s="3">
+        <v>4.0149170683248803E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <v>3.1378995347075E-2</v>
+      </c>
+      <c r="B78" s="3">
+        <v>4.6441451549996803E-3</v>
+      </c>
+      <c r="C78" s="3">
+        <v>4.1912236452322997E-2</v>
+      </c>
+      <c r="D78" s="3">
+        <v>8.4466024422860907E-3</v>
+      </c>
+      <c r="E78" s="3">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="F78" s="3">
+        <v>4.3189582166166703E-3</v>
+      </c>
+      <c r="G78" s="3">
+        <v>2.37356594586151E-2</v>
+      </c>
+      <c r="H78" s="3">
+        <v>4.3728223932450504E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <v>2.9962092575819201E-2</v>
+      </c>
+      <c r="B79" s="3">
+        <v>4.3591300625535397E-3</v>
+      </c>
+      <c r="C79" s="3">
+        <v>4.1476590891557599E-2</v>
+      </c>
+      <c r="D79" s="3">
+        <v>8.3508813853177405E-3</v>
+      </c>
+      <c r="E79" s="3">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="F79" s="3">
+        <v>4.0791957488200302E-3</v>
+      </c>
+      <c r="G79" s="3">
+        <v>2.4288093875897698E-2</v>
+      </c>
+      <c r="H79" s="3">
+        <v>4.7931384574506604E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
+        <v>2.78539973292307E-2</v>
+      </c>
+      <c r="B80" s="3">
+        <v>3.9810061648486196E-3</v>
+      </c>
+      <c r="C80" s="3">
+        <v>4.0278392013620601E-2</v>
+      </c>
+      <c r="D80" s="3">
+        <v>8.3970753508035203E-3</v>
+      </c>
+      <c r="E80" s="3">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="F80" s="3">
+        <v>3.9572218472342701E-3</v>
+      </c>
+      <c r="G80" s="3">
+        <v>2.46922473303752E-2</v>
+      </c>
+      <c r="H80" s="3">
+        <v>5.0702642929123902E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <v>2.8742006072579498E-2</v>
+      </c>
+      <c r="B81" s="3">
+        <v>3.7621363544598102E-3</v>
+      </c>
+      <c r="C81" s="3">
+        <v>3.8661119137853799E-2</v>
+      </c>
+      <c r="D81" s="3">
+        <v>8.4250970519382101E-3</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="F81" s="3">
+        <v>3.8574545782443198E-3</v>
+      </c>
+      <c r="G81" s="3">
+        <v>2.50501549132899E-2</v>
+      </c>
+      <c r="H81" s="3">
+        <v>5.4092186851562498E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>3.0075997146335701E-2</v>
+      </c>
+      <c r="B82" s="3">
+        <v>3.8515306397318601E-3</v>
+      </c>
+      <c r="C82" s="3">
+        <v>3.7631322027066802E-2</v>
+      </c>
+      <c r="D82" s="3">
+        <v>8.7393169721731601E-3</v>
+      </c>
+      <c r="E82" s="3">
+        <v>2.07E-2</v>
+      </c>
+      <c r="F82" s="3">
+        <v>3.91964853059781E-3</v>
+      </c>
+      <c r="G82" s="3">
+        <v>2.5303655086982201E-2</v>
+      </c>
+      <c r="H82" s="3">
+        <v>5.6290444749318002E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <v>3.0535114943174201E-2</v>
+      </c>
+      <c r="B83" s="3">
+        <v>4.0434415177107198E-3</v>
+      </c>
+      <c r="C83" s="3">
+        <v>3.7716251354449601E-2</v>
+      </c>
+      <c r="D83" s="3">
+        <v>8.9000267561307692E-3</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2.07E-2</v>
+      </c>
+      <c r="F83" s="3">
+        <v>4.1287329333342402E-3</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2.5822646118584699E-2</v>
+      </c>
+      <c r="H83" s="3">
+        <v>5.8465363708167196E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
+        <v>3.2505112309042697E-2</v>
+      </c>
+      <c r="B84" s="3">
+        <v>4.3535960861635203E-3</v>
+      </c>
+      <c r="C84" s="3">
+        <v>3.6545404210546799E-2</v>
+      </c>
+      <c r="D84" s="3">
+        <v>8.7337591113494997E-3</v>
+      </c>
+      <c r="E84" s="3">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="F84" s="3">
+        <v>4.2677384296381403E-3</v>
+      </c>
+      <c r="G84" s="3">
+        <v>2.5713010118598299E-2</v>
+      </c>
+      <c r="H84" s="3">
+        <v>6.0147242124002796E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <v>3.5278812089969899E-2</v>
+      </c>
+      <c r="B85" s="3">
+        <v>4.7448008835169302E-3</v>
+      </c>
+      <c r="C85" s="3">
+        <v>3.5801126955130498E-2</v>
+      </c>
+      <c r="D85" s="3">
+        <v>8.4747013607879094E-3</v>
+      </c>
+      <c r="E85" s="3">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="F85" s="3">
+        <v>4.4087124647994302E-3</v>
+      </c>
+      <c r="G85" s="3">
+        <v>2.5003871766632099E-2</v>
+      </c>
+      <c r="H85" s="3">
+        <v>6.1066355046597602E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="3">
+        <v>3.6602209103473997E-2</v>
+      </c>
+      <c r="B86" s="3">
+        <v>4.90242866477438E-3</v>
+      </c>
+      <c r="C86" s="3">
+        <v>3.55756552694226E-2</v>
+      </c>
+      <c r="D86" s="3">
+        <v>8.8507370102666495E-3</v>
+      </c>
+      <c r="E86" s="3">
+        <v>2.18E-2</v>
+      </c>
+      <c r="F86" s="3">
+        <v>4.8126576067659896E-3</v>
+      </c>
+      <c r="G86" s="3">
+        <v>2.5013119291359302E-2</v>
+      </c>
+      <c r="H86" s="3">
+        <v>6.1061919525458403E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <v>3.7723904965138999E-2</v>
+      </c>
+      <c r="B87" s="3">
+        <v>4.9039818414736598E-3</v>
+      </c>
+      <c r="C87" s="3">
+        <v>3.5195159980632197E-2</v>
+      </c>
+      <c r="D87" s="3">
+        <v>8.9255453477168501E-3</v>
+      </c>
+      <c r="E87" s="3">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="F87" s="3">
+        <v>5.1132174408959896E-3</v>
+      </c>
+      <c r="G87" s="3">
+        <v>2.5379345027576199E-2</v>
+      </c>
+      <c r="H87" s="3">
+        <v>5.9637781342875302E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
+        <v>3.8251473394000701E-2</v>
+      </c>
+      <c r="B88" s="3">
+        <v>4.8378914807664496E-3</v>
+      </c>
+      <c r="C88" s="3">
+        <v>3.4653708493766901E-2</v>
+      </c>
+      <c r="D88" s="3">
+        <v>8.7911571424987602E-3</v>
+      </c>
+      <c r="E88" s="3">
+        <v>2.23E-2</v>
+      </c>
+      <c r="F88" s="3">
+        <v>5.23775009131073E-3</v>
+      </c>
+      <c r="G88" s="3">
+        <v>2.56376710516232E-2</v>
+      </c>
+      <c r="H88" s="3">
+        <v>5.6294284602711204E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="3">
+        <v>3.8336888779692803E-2</v>
+      </c>
+      <c r="B89" s="3">
+        <v>4.9457945446601198E-3</v>
+      </c>
+      <c r="C89" s="3">
+        <v>3.4111941034259602E-2</v>
+      </c>
+      <c r="D89" s="3">
+        <v>9.0649440223504706E-3</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2.24E-2</v>
+      </c>
+      <c r="F89" s="3">
+        <v>5.4372970483292501E-3</v>
+      </c>
+      <c r="G89" s="3">
+        <v>2.6139356449859701E-2</v>
+      </c>
+      <c r="H89" s="3">
+        <v>5.4662797013989E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="3">
+        <v>3.7625837002672802E-2</v>
+      </c>
+      <c r="B90" s="3">
+        <v>4.9574636198872202E-3</v>
+      </c>
+      <c r="C90" s="3">
+        <v>3.4253522868254699E-2</v>
+      </c>
+      <c r="D90" s="3">
+        <v>9.2672759252571991E-3</v>
+      </c>
+      <c r="E90" s="3">
+        <v>2.23E-2</v>
+      </c>
+      <c r="F90" s="3">
+        <v>5.54280252297637E-3</v>
+      </c>
+      <c r="G90" s="3">
+        <v>2.64128314791418E-2</v>
+      </c>
+      <c r="H90" s="3">
+        <v>5.24114807924297E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="3">
+        <v>3.5843303074199202E-2</v>
+      </c>
+      <c r="B91" s="3">
+        <v>5.0470939610091003E-3</v>
+      </c>
+      <c r="C91" s="3">
+        <v>3.4442341333348399E-2</v>
+      </c>
+      <c r="D91" s="3">
+        <v>9.2599720617427706E-3</v>
+      </c>
+      <c r="E91" s="3">
+        <v>2.23E-2</v>
+      </c>
+      <c r="F91" s="3">
+        <v>5.5036087533845901E-3</v>
+      </c>
+      <c r="G91" s="3">
+        <v>2.6201911283987401E-2</v>
+      </c>
+      <c r="H91" s="3">
+        <v>5.0262772546905404E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="3">
+        <v>3.5229287443145303E-2</v>
+      </c>
+      <c r="B92" s="3">
+        <v>5.2589911823118698E-3</v>
+      </c>
+      <c r="C92" s="3">
+        <v>3.4411166314050903E-2</v>
+      </c>
+      <c r="D92" s="3">
+        <v>8.9711659062099592E-3</v>
+      </c>
+      <c r="E92" s="3">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="F92" s="3">
+        <v>5.2748786156597699E-3</v>
+      </c>
+      <c r="G92" s="3">
+        <v>2.58735971120173E-2</v>
+      </c>
+      <c r="H92" s="3">
+        <v>4.8969609642259002E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="3">
+        <v>3.4510476454017697E-2</v>
+      </c>
+      <c r="B93" s="3">
+        <v>5.4054851768209804E-3</v>
+      </c>
+      <c r="C93" s="3">
+        <v>3.3806637110966001E-2</v>
+      </c>
+      <c r="D93" s="3">
+        <v>8.6920768533120703E-3</v>
+      </c>
+      <c r="E93" s="3">
+        <v>2.06E-2</v>
+      </c>
+      <c r="F93" s="3">
+        <v>5.0410696366364098E-3</v>
+      </c>
+      <c r="G93" s="3">
+        <v>2.4848147369517098E-2</v>
+      </c>
+      <c r="H93" s="3">
+        <v>4.6489589891256702E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="3">
+        <v>3.3222981352896003E-2</v>
+      </c>
+      <c r="B94" s="3">
+        <v>5.5793175760004204E-3</v>
+      </c>
+      <c r="C94" s="3">
+        <v>3.2771690342705502E-2</v>
+      </c>
+      <c r="D94" s="3">
+        <v>8.37506416592111E-3</v>
+      </c>
+      <c r="E94" s="3">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="F94" s="3">
+        <v>4.7702573660676397E-3</v>
+      </c>
+      <c r="G94" s="3">
+        <v>2.47943346805178E-2</v>
+      </c>
+      <c r="H94" s="3">
+        <v>4.5446082732766803E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="3">
+        <v>3.1704861921923101E-2</v>
+      </c>
+      <c r="B95" s="3">
+        <v>5.7395376437296402E-3</v>
+      </c>
+      <c r="C95" s="3">
+        <v>3.0929497862612999E-2</v>
+      </c>
+      <c r="D95" s="3">
+        <v>7.75367755019888E-3</v>
+      </c>
+      <c r="E95" s="3">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="F95" s="3">
+        <v>4.6777162770114296E-3</v>
+      </c>
+      <c r="G95" s="3">
+        <v>2.4301496623201701E-2</v>
+      </c>
+      <c r="H95" s="3">
+        <v>4.2305915042170896E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="3">
+        <v>3.10000416245533E-2</v>
+      </c>
+      <c r="B96" s="3">
+        <v>5.8868636490781003E-3</v>
+      </c>
+      <c r="C96" s="3">
+        <v>2.8553136565817001E-2</v>
+      </c>
+      <c r="D96" s="3">
+        <v>7.00521686331708E-3</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1.84E-2</v>
+      </c>
+      <c r="F96" s="3">
+        <v>4.2436731472445003E-3</v>
+      </c>
+      <c r="G96" s="3">
+        <v>2.2618760663269399E-2</v>
+      </c>
+      <c r="H96" s="3">
+        <v>3.9074056440890599E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="3">
+        <v>3.0067701141456599E-2</v>
+      </c>
+      <c r="B97" s="3">
+        <v>6.1122422113770204E-3</v>
+      </c>
+      <c r="C97" s="3">
+        <v>2.6723020903182099E-2</v>
+      </c>
+      <c r="D97" s="3">
+        <v>6.6446989965070003E-3</v>
+      </c>
+      <c r="E97" s="3">
+        <v>1.78E-2</v>
+      </c>
+      <c r="F97" s="3">
+        <v>4.1836252766808499E-3</v>
+      </c>
+      <c r="G97" s="3">
+        <v>2.1738715324167299E-2</v>
+      </c>
+      <c r="H97" s="3">
+        <v>3.74110404641849E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" s="3">
+        <v>2.9046795709320901E-2</v>
+      </c>
+      <c r="B98" s="3">
+        <v>6.2776123186592302E-3</v>
+      </c>
+      <c r="C98" s="3">
+        <v>2.48218385481297E-2</v>
+      </c>
+      <c r="D98" s="3">
+        <v>6.24075162711254E-3</v>
+      </c>
+      <c r="E98" s="3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F98" s="3">
+        <v>4.2458254525567897E-3</v>
+      </c>
+      <c r="G98" s="3">
+        <v>2.09685259021609E-2</v>
+      </c>
+      <c r="H98" s="3">
+        <v>3.9463088489760196E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="3">
+        <v>2.7954342736067901E-2</v>
+      </c>
+      <c r="B99" s="3">
+        <v>6.43992688790972E-3</v>
+      </c>
+      <c r="C99" s="3">
+        <v>2.28395738214799E-2</v>
+      </c>
+      <c r="D99" s="3">
+        <v>5.7265375015901898E-3</v>
+      </c>
+      <c r="E99" s="3">
+        <v>1.66E-2</v>
+      </c>
+      <c r="F99" s="3">
+        <v>4.2431090219116297E-3</v>
+      </c>
+      <c r="G99" s="3">
+        <v>2.0325889351825902E-2</v>
+      </c>
+      <c r="H99" s="3">
+        <v>3.9998838713267201E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="3">
+        <v>2.7581482778870001E-2</v>
+      </c>
+      <c r="B100" s="3">
+        <v>6.6822634771466598E-3</v>
+      </c>
+      <c r="C100" s="3">
+        <v>2.16246944110851E-2</v>
+      </c>
+      <c r="D100" s="3">
+        <v>5.6280172264573502E-3</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="F100" s="3">
+        <v>4.2342659212288303E-3</v>
+      </c>
+      <c r="G100" s="3">
+        <v>1.98561486970091E-2</v>
+      </c>
+      <c r="H100" s="3">
+        <v>4.0993244081814198E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>